--- a/examples/data/model_points_wide.xlsx
+++ b/examples/data/model_points_wide.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ADB_benefit</t>
+          <t>adb_benefit</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>HOSP_benefit</t>
+          <t>hosp_benefit</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>CANCER_benefit</t>
+          <t>cancer_benefit</t>
         </is>
       </c>
     </row>

--- a/examples/data/model_points_wide.xlsx
+++ b/examples/data/model_points_wide.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>monthly_premium</t>
+          <t>level_premium</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">

--- a/examples/data/model_points_wide.xlsx
+++ b/examples/data/model_points_wide.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>policy_id</t>
+          <t>mp_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">

--- a/examples/data/model_points_wide.xlsx
+++ b/examples/data/model_points_wide.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>adb_benefit</t>
+          <t>ADB_benefit</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>hosp_benefit</t>
+          <t>INPATIENT_benefit</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>cancer_benefit</t>
+          <t>CANCER_benefit</t>
         </is>
       </c>
     </row>

--- a/examples/data/model_points_wide.xlsx
+++ b/examples/data/model_points_wide.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>death_benefit</t>
+          <t>DEATH_GENERAL_benefit</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">

--- a/examples/data/model_points_wide.xlsx
+++ b/examples/data/model_points_wide.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>DEATH_GENERAL_benefit</t>
+          <t>DEATH_benefit</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
